--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>112.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.0%</t>
+          <t>495.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-474.7%</t>
+          <t>-474.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-195.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.1%</t>
+          <t>-192.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-197.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-139.5%</t>
+          <t>-120.4%</t>
         </is>
       </c>
     </row>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.528723700694423</v>
+        <v>-9.845132691325576</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6348561262422536</v>
+        <v>-0.7614197224947148</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.777823654458307</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.301927873621089</v>
+        <v>-9.618336864252242</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5415040212508124</v>
+        <v>-0.668067617503274</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.709709709836762</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.01801914269234</v>
+        <v>-9.334428133323494</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4222068246406767</v>
+        <v>-0.5487704208931379</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.709709709836762</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.771031892499389</v>
+        <v>-9.087440883130542</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3331491869573613</v>
+        <v>-0.4597127832098225</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.46272245964381</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.507195025295319</v>
+        <v>-8.823604015926472</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2374979213886408</v>
+        <v>-0.364061517641102</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.46272245964381</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.239953224426921</v>
+        <v>-8.556362215058074</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1324357615406555</v>
+        <v>-0.2589993577931167</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.46272245964381</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.964144061026437</v>
+        <v>-8.28055305165759</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.02241241115392256</v>
+        <v>-0.1489760074063837</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.373703151365077</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.695076473259458</v>
+        <v>-8.01148546389061</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.08588313009836268</v>
+        <v>-0.04068046615409804</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.104635563598098</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.431016534936662</v>
+        <v>-7.747425525567814</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.1782467892657289</v>
+        <v>0.05168319301326818</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.840575625275301</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.723936911431823</v>
+        <v>-7.040345902062976</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.4582916050073633</v>
+        <v>0.3317280087549026</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.840575625275301</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.474295881445872</v>
+        <v>-6.790704872077024</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.5584916408895855</v>
+        <v>0.4319280446371248</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.59093459528935</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.219753982104796</v>
+        <v>-6.536162972735948</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.6596752218467725</v>
+        <v>0.5331116255943122</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.336392695948274</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.986272759875198</v>
+        <v>-6.302681750506349</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.7609921395764645</v>
+        <v>0.6344285433240038</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.102911473718676</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.806564229731325</v>
+        <v>-6.122973220362477</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.8299833413210544</v>
+        <v>0.7034197450685937</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.045739969555979</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.674288756100439</v>
+        <v>-5.99069774673159</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.8782610175204359</v>
+        <v>0.7516974212679752</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9134644959250928</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.483689081427286</v>
+        <v>-5.800098072058438</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.9573159480773339</v>
+        <v>0.8307523518248732</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.72286482125194</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.234689282743705</v>
+        <v>-5.551098273374857</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.069822208774425</v>
+        <v>0.9432586125219644</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.72286482125194</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.34027927251681</v>
+        <v>-5.656688263147961</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.8996102832659645</v>
+        <v>0.7730466870135038</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8284548110250443</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.359014174635407</v>
+        <v>-5.675423165266558</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.9406606642956121</v>
+        <v>0.8140970680431514</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8284548110250443</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.082275999964594</v>
+        <v>-5.398684990595745</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.054734946149932</v>
+        <v>0.9281713498974713</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.6466381499151185</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.955383593529524</v>
+        <v>-5.271792584160675</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.096777922470482</v>
+        <v>0.970214326218021</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5197457434800485</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.767796085619597</v>
+        <v>-5.084205076250749</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.164852313539359</v>
+        <v>1.038288717286898</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5197457434800485</v>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.525647692165739</v>
+        <v>-4.84205668279689</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.276174025302045</v>
+        <v>1.149610429049585</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5197457434800485</v>
@@ -45573,10 +45573,10 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.462418320397391</v>
+        <v>-4.778827311028542</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.29599789446858</v>
+        <v>1.169434298216119</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5197457434800485</v>
@@ -45596,10 +45596,10 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.275930628020385</v>
+        <v>-4.592339618651536</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.368091065429959</v>
+        <v>1.241527469177498</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.3332580511030423</v>
@@ -45619,10 +45619,10 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.254781429116941</v>
+        <v>-4.571190419748093</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.384251723228662</v>
+        <v>1.257688126976201</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3121088521995989</v>
@@ -45642,10 +45642,10 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.011015987133497</v>
+        <v>-4.327424977764649</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.47753860836909</v>
+        <v>1.35097501211663</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3121088521995989</v>
@@ -45665,10 +45665,10 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.746987919940237</v>
+        <v>-4.063396910571388</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.58527414916641</v>
+        <v>1.45871055291395</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1102434533836454</v>
@@ -45688,10 +45688,10 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.497137525991163</v>
+        <v>-3.813546516622313</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.677956381729742</v>
+        <v>1.551392785477282</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1102434533836454</v>
@@ -45711,10 +45711,10 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.193570036987184</v>
+        <v>-3.509979027618335</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.802982500851982</v>
+        <v>1.676418904599522</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1102434533836454</v>
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.719785815710063</v>
+        <v>3.402071660005716</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.131084486970641</v>
+        <v>-3.129472239803401</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.841304226913153</v>
+        <v>1.84194912578005</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.04775790336710228</v>
+        <v>0.270263334431289</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.065439703994897</v>
+        <v>3.256252446673932</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.2%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.3%</t>
+          <t>494.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-474.5%</t>
+          <t>-505.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-195.0%</t>
+          <t>-194.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-192.0%</t>
+          <t>-204.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-197.0%</t>
+          <t>-227.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.4%</t>
+          <t>-138.8%</t>
         </is>
       </c>
     </row>
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.129472239803401</v>
+        <v>-3.436499118766321</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.84194912578005</v>
+        <v>1.719138374194882</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.270263334431289</v>
+        <v>-0.036763544531631</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.256252446673932</v>
+        <v>3.072036319296179</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.402071660005716</v>
+        <v>3.402071660005714</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-30.3%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>129.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.4%</t>
+          <t>494.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-194.3%</t>
+          <t>-194.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.8%</t>
+          <t>-165.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1921"/>
+  <dimension ref="A1:G1922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495503</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207817</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006537</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.402071660005714</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45744,6 +45744,29 @@
       </c>
       <c r="G1921" t="n">
         <v>3.072036319296179</v>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" s="2" t="n">
+        <v>45384</v>
+      </c>
+      <c r="B1922" t="n">
+        <v>3.380011470014373</v>
+      </c>
+      <c r="C1922" t="n">
+        <v>2.813007483757141</v>
+      </c>
+      <c r="D1922" t="n">
+        <v>-3.436499118766321</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>1.719138374194882</v>
+      </c>
+      <c r="F1922" t="n">
+        <v>-0.036763544531631</v>
+      </c>
+      <c r="G1922" t="n">
+        <v>2.806071280743509</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-2.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.0%</t>
+          <t>129.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.1%</t>
+          <t>-606.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.1%</t>
+          <t>499.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.2%</t>
+          <t>-475.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-242.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-194.2%</t>
+          <t>-82.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-197.8%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.4%</t>
+          <t>-137.6%</t>
         </is>
       </c>
     </row>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495503</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.958683943966089</v>
+        <v>-2.980494241859249</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.954260535852063</v>
+        <v>1.945536416694799</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.324177015085912</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.80983243085875</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130021</v>
+        <v>3.287377576130022</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.68182736532426</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.662878349419668</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.666678007653247</v>
+        <v>-3.688488305546408</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.670711019188333</v>
+        <v>1.661986900031069</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207817</v>
+        <v>3.305316798207819</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.098483800803034</v>
+        <v>-4.120294098696196</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.484321589395822</v>
+        <v>1.475597470238558</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310988</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.424916329670778</v>
+        <v>-4.446726627563939</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.342033352850815</v>
+        <v>1.333309233693551</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006537</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.426480480781081</v>
+        <v>-4.448290778674242</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.33998828406266</v>
+        <v>1.331264164905395</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.31108639130943</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.790106725681395</v>
+        <v>-4.811917023574556</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.201025346336776</v>
+        <v>1.192301227179511</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.304715716970911</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.787679661152676</v>
+        <v>-4.809489959045838</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.201250687154094</v>
+        <v>1.19252656799683</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.9246304134785115</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330528</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.196268438333354</v>
+        <v>-5.218078736226516</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.036576720296582</v>
+        <v>1.027852601139318</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.33321919065919</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191743</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.609250922474448</v>
+        <v>-5.631061220367609</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8665691591116054</v>
+        <v>0.8578450399543409</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.33321919065919</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108645</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.025642796761446</v>
+        <v>-6.047453094654607</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6980064600056837</v>
+        <v>0.6892823408484192</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.33321919065919</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097827</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.40231980729129</v>
+        <v>-6.424130105184451</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5575943464624249</v>
+        <v>0.5488702273051604</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.33321919065919</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094123</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.416034671616401</v>
+        <v>-6.437844969509563</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5482079658780754</v>
+        <v>0.539483846720811</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.33321919065919</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199292</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.728859470861381</v>
+        <v>-6.750669768754542</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4214829662350845</v>
+        <v>0.4127588470778201</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.33321919065919</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.733672509326718</v>
+        <v>-6.755482807219879</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.423336726778158</v>
+        <v>0.4146126076208936</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.334765825361976</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923094</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.167021617436954</v>
+        <v>-7.188831915330115</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2459707789996606</v>
+        <v>0.2372466598423961</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.334765825361976</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297756</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.550023006179585</v>
+        <v>-7.571833304072746</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09266812218102416</v>
+        <v>0.08394400302375971</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.334765825361976</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317623</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.925008332350862</v>
+        <v>-7.946818630244024</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05475449231605678</v>
+        <v>-0.06347861147332123</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.709751151533253</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737177</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.284538654854863</v>
+        <v>-8.306348952748024</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1932163180196071</v>
+        <v>-0.2019404371768716</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.709751151533253</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.50317028234132</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.610938683519876</v>
+        <v>-8.632748981413037</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3158603095284351</v>
+        <v>-0.3245844286856996</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.036151180198266</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776683</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.604462536726317</v>
+        <v>-8.626272834619478</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3102281001892422</v>
+        <v>-0.3189522193465066</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.029675033404706</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.600771611769906</v>
+        <v>-8.622581909663067</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3087517302066778</v>
+        <v>-0.3174758493639422</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.029675033404706</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.80502978709977</v>
+        <v>-8.826840084992931</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3849418032199812</v>
+        <v>-0.3936659223772456</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.157313978018695</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.965668813588135</v>
+        <v>-8.987479111481296</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4447148593308912</v>
+        <v>-0.4534389784881556</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.272047451021091</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.892198981920686</v>
+        <v>-8.914009279813847</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3999552251704905</v>
+        <v>-0.408679344327755</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.198577619353642</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.067323399307229</v>
+        <v>-9.08913369720039</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4554497713775909</v>
+        <v>-0.4641738905348554</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.373702036740186</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.301775493321719</v>
+        <v>-9.32358579121488</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.556449773884983</v>
+        <v>-0.5651738930422474</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.373702036740186</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.589579337858957</v>
+        <v>-9.611389635752118</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6782435024738542</v>
+        <v>-0.6869676216311187</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.661505881277424</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.819403785022782</v>
+        <v>-9.841214082915943</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7690574915008281</v>
+        <v>-0.7777816106580926</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.824153418347585</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.05143270475904</v>
+        <v>-10.07324300265221</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.859175330766218</v>
+        <v>-0.8678994499234824</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.886166115536008</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.999417190790231</v>
+        <v>-10.02122748868339</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8343787894922921</v>
+        <v>-0.8431029086495565</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.886166115536008</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.14108903251435</v>
+        <v>-10.16289933040751</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8925227530806819</v>
+        <v>-0.9012468722379463</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.886166115536008</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.69156815841072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.23999577297363</v>
+        <v>-10.26180607086679</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9170320390995195</v>
+        <v>-0.9257561582567839</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.985072855995284</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.67683797424058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.04084366573653</v>
+        <v>-10.06265396362969</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8504223298513636</v>
+        <v>-0.859146449008628</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.81975033004547</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.814998513017118</v>
+        <v>-9.836808810910279</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7505051957273907</v>
+        <v>-0.7592293148846552</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.777823654458307</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.845132691325576</v>
+        <v>-9.550533998587584</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7614197224947148</v>
+        <v>-0.6435802453995181</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.777823654458307</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.618336864252242</v>
+        <v>-9.32373817151425</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.668067617503274</v>
+        <v>-0.5502281404080769</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.709709709836762</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.334428133323494</v>
+        <v>-9.039829440585502</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5487704208931379</v>
+        <v>-0.4309309437979412</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.709709709836762</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.728574354425332</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.087440883130542</v>
+        <v>-8.79284219039255</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4597127832098225</v>
+        <v>-0.3418733061146257</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.46272245964381</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.823604015926472</v>
+        <v>-8.52900532318848</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.364061517641102</v>
+        <v>-0.2462220405459052</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.46272245964381</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.556362215058074</v>
+        <v>-8.261763522320082</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2589993577931167</v>
+        <v>-0.14115988069792</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.46272245964381</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.28055305165759</v>
+        <v>-7.985954358919598</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1489760074063837</v>
+        <v>-0.03113653031118702</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.373703151365077</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567248</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.01148546389061</v>
+        <v>-7.716886771152619</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.04068046615409804</v>
+        <v>0.07715901094109823</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.104635563598098</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.747425525567814</v>
+        <v>-7.452826832829823</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.05168319301326818</v>
+        <v>0.1695226701084644</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.840575625275301</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.83324917230973</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.040345902062976</v>
+        <v>-6.745747209324985</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.3317280087549026</v>
+        <v>0.4495674858500989</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.840575625275301</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.790704872077024</v>
+        <v>-6.496106179339033</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.4319280446371248</v>
+        <v>0.549767521732321</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.59093459528935</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.536162972735948</v>
+        <v>-6.241564279997958</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.5331116255943122</v>
+        <v>0.6509511026895081</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.336392695948274</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.302681750506349</v>
+        <v>-6.008083057768359</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.6344285433240038</v>
+        <v>0.7522680204192</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.102911473718676</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.122973220362477</v>
+        <v>-5.828374527624486</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.7034197450685937</v>
+        <v>0.82125922216379</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.045739969555979</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.99069774673159</v>
+        <v>-5.6960990539936</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.7516974212679752</v>
+        <v>0.8695368983631715</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9134644959250928</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.800098072058438</v>
+        <v>-5.505499379320447</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.8307523518248732</v>
+        <v>0.9485918289200694</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.72286482125194</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.551098273374857</v>
+        <v>-5.256499580636866</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.9432586125219644</v>
+        <v>1.06109808961716</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.72286482125194</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.656688263147961</v>
+        <v>-5.362089570409971</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.7730466870135038</v>
+        <v>0.8908861641087</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8284548110250443</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.675423165266558</v>
+        <v>-5.380824472528568</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.8140970680431514</v>
+        <v>0.9319365451383477</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8284548110250443</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.035050646285567</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.398684990595745</v>
+        <v>-5.104086297857755</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9281713498974713</v>
+        <v>0.9930597028287171</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.6466381499151185</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.700018880500446</v>
+        <v>2.647067756336496</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.026336660032089</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.271792584160675</v>
+        <v>-4.977193891422685</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.970214326218021</v>
+        <v>1.035102679149267</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5197457434800485</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.76744033810801</v>
+        <v>2.71448921394406</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.019376047936996</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.084205076250749</v>
+        <v>-4.789606383512758</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.038288717286898</v>
+        <v>1.103177070218145</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5197457434800485</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.760479726012917</v>
+        <v>2.707528601848967</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.086789526482089</v>
+        <v>3.033838402318139</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.84205668279689</v>
+        <v>-4.5474579900589</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.149610429049585</v>
+        <v>1.214498781980831</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5197457434800485</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.77494208039406</v>
+        <v>2.72199095623011</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.081321646941284</v>
+        <v>3.028370522777334</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.778827311028542</v>
+        <v>-4.484228618290552</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.169434298216119</v>
+        <v>1.234322651147365</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5197457434800485</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.769474200853255</v>
+        <v>2.716523076689305</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.078819740951861</v>
+        <v>3.025868616787911</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.592339618651536</v>
+        <v>-4.297740925913546</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.241527469177498</v>
+        <v>1.306415822108745</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.3332580511030423</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.878864910290036</v>
+        <v>2.825913786126086</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.086520719189187</v>
+        <v>3.033569595025236</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.571190419748093</v>
+        <v>-4.276591727010103</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.257688126976201</v>
+        <v>1.322576479907447</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3121088521995989</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.899255407869427</v>
+        <v>2.846304283705477</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.082301427536237</v>
+        <v>3.029350303372287</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.327424977764649</v>
+        <v>-4.032826285026658</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.35097501211663</v>
+        <v>1.415863365047876</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3121088521995989</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.895036116216478</v>
+        <v>2.842084992052528</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.084425741456253</v>
+        <v>3.031474617292303</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.063396910571388</v>
+        <v>-3.768798217833398</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.45871055291395</v>
+        <v>1.523598905845196</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1102434533836454</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.018279669426066</v>
+        <v>2.965328545262116</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.077167816439955</v>
+        <v>3.024216692276005</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.813546516622313</v>
+        <v>-3.518947823884324</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.551392785477282</v>
+        <v>1.616281138408528</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1102434533836454</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.011021744409768</v>
+        <v>2.958070620245818</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.080766939960604</v>
+        <v>3.027815815796654</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.509979027618335</v>
+        <v>-3.215380334880345</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.676418904599522</v>
+        <v>1.741307257530768</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1102434533836454</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.014620867930417</v>
+        <v>2.961669743766467</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862991</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.094094446015158</v>
+        <v>3.041143321851207</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.436499118766321</v>
+        <v>-3.141900426028331</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.719138374194882</v>
+        <v>1.784026727126127</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.036763544531631</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.072036319296179</v>
+        <v>3.019085195132229</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.380011470014373</v>
+        <v>3.765189293763097</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.813007483757141</v>
+        <v>3.091332055832155</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.436499118766321</v>
+        <v>-3.141900426028331</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.719138374194882</v>
+        <v>1.784026727126127</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.036763544531631</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.806071280743509</v>
+        <v>3.084395852818523</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-27.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.3%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-606.2%</t>
+          <t>-604.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.7%</t>
+          <t>494.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-475.8%</t>
+          <t>-501.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.9%</t>
+          <t>-242.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-82.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.8%</t>
+          <t>-202.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-160.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.7%</t>
+          <t>-249.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-162.9%</t>
         </is>
       </c>
     </row>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.980494241859249</v>
+        <v>-2.958683943966089</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.945536416694799</v>
+        <v>1.954260535852063</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.1416338455902526</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.324177015085912</v>
+        <v>-3.302366717192751</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.80983243085875</v>
+        <v>1.818556550016014</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.2495398976174708</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.68182736532426</v>
+        <v>-3.660017067431099</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.662878349419668</v>
+        <v>1.671602468576933</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.6071902478558189</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.688488305546408</v>
+        <v>-3.666678007653247</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.661986900031069</v>
+        <v>1.670711019188333</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.6071902478558189</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207819</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.120294098696196</v>
+        <v>-4.098483800803034</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.475597470238558</v>
+        <v>1.484321589395822</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.7436077442970859</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310988</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.446726627563939</v>
+        <v>-4.424916329670778</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.333309233693551</v>
+        <v>1.342033352850815</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.826075994804234</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006538</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.448290778674242</v>
+        <v>-4.426480480781081</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.331264164905395</v>
+        <v>1.33998828406266</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.826075994804234</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130943</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.811917023574556</v>
+        <v>-4.790106725681395</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.192301227179511</v>
+        <v>1.201025346336776</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9242976316713598</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970911</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.809489959045838</v>
+        <v>-4.787679661152676</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.19252656799683</v>
+        <v>1.201250687154094</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.9246304134785115</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330528</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.218078736226516</v>
+        <v>-5.196268438333354</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.027852601139318</v>
+        <v>1.036576720296582</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.33321919065919</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.631061220367609</v>
+        <v>-5.609250922474448</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8578450399543409</v>
+        <v>0.8665691591116054</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.33321919065919</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.047453094654607</v>
+        <v>-6.025642796761446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6892823408484192</v>
+        <v>0.6980064600056837</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.33321919065919</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097827</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.424130105184451</v>
+        <v>-6.40231980729129</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5488702273051604</v>
+        <v>0.5575943464624249</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.33321919065919</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094123</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.437844969509563</v>
+        <v>-6.416034671616401</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.539483846720811</v>
+        <v>0.5482079658780754</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.33321919065919</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199292</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.750669768754542</v>
+        <v>-6.728859470861381</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4127588470778201</v>
+        <v>0.4214829662350845</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.33321919065919</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.755482807219879</v>
+        <v>-6.733672509326718</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.4146126076208936</v>
+        <v>0.423336726778158</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.334765825361976</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923094</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.188831915330115</v>
+        <v>-7.167021617436954</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2372466598423961</v>
+        <v>0.2459707789996606</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.334765825361976</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297756</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.571833304072746</v>
+        <v>-7.550023006179585</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.08394400302375971</v>
+        <v>0.09266812218102416</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.334765825361976</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317623</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.946818630244024</v>
+        <v>-7.925008332350862</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.06347861147332123</v>
+        <v>-0.05475449231605678</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.709751151533253</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737177</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.306348952748024</v>
+        <v>-8.284538654854863</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2019404371768716</v>
+        <v>-0.1932163180196071</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.709751151533253</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234132</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.632748981413037</v>
+        <v>-8.610938683519876</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3245844286856996</v>
+        <v>-0.3158603095284351</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.036151180198266</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776683</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.626272834619478</v>
+        <v>-8.604462536726317</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3189522193465066</v>
+        <v>-0.3102281001892422</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.029675033404706</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407496</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.622581909663067</v>
+        <v>-8.600771611769906</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3174758493639422</v>
+        <v>-0.3087517302066778</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.029675033404706</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.826840084992931</v>
+        <v>-8.80502978709977</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3936659223772456</v>
+        <v>-0.3849418032199812</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.157313978018695</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.987479111481296</v>
+        <v>-8.965668813588135</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4534389784881556</v>
+        <v>-0.4447148593308912</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.272047451021091</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.914009279813847</v>
+        <v>-8.892198981920686</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.408679344327755</v>
+        <v>-0.3999552251704905</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.198577619353642</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.08913369720039</v>
+        <v>-9.067323399307229</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4641738905348554</v>
+        <v>-0.4554497713775909</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.373702036740186</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.32358579121488</v>
+        <v>-9.301775493321719</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5651738930422474</v>
+        <v>-0.556449773884983</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.373702036740186</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.611389635752118</v>
+        <v>-9.589579337858957</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6869676216311187</v>
+        <v>-0.6782435024738542</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.661505881277424</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.841214082915943</v>
+        <v>-9.819403785022782</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7777816106580926</v>
+        <v>-0.7690574915008281</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.824153418347585</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.07324300265221</v>
+        <v>-10.05143270475904</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.8678994499234824</v>
+        <v>-0.859175330766218</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.886166115536008</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.02122748868339</v>
+        <v>-9.999417190790231</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8431029086495565</v>
+        <v>-0.8343787894922921</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.886166115536008</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.16289933040751</v>
+        <v>-10.14108903251435</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9012468722379463</v>
+        <v>-0.8925227530806819</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.886166115536008</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69156815841072</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.26180607086679</v>
+        <v>-10.23999577297363</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9257561582567839</v>
+        <v>-0.9170320390995195</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.985072855995284</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67683797424058</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.06265396362969</v>
+        <v>-10.04084366573653</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.859146449008628</v>
+        <v>-0.8504223298513636</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.81975033004547</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085282</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.836808810910279</v>
+        <v>-9.814998513017118</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7592293148846552</v>
+        <v>-0.7505051957273907</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.777823654458307</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.550533998587584</v>
+        <v>-9.528723700694423</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6435802453995181</v>
+        <v>-0.6348561262422536</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.777823654458307</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116219</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.32373817151425</v>
+        <v>-9.301927873621089</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5502281404080769</v>
+        <v>-0.5415040212508124</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.709709709836762</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081571</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.039829440585502</v>
+        <v>-9.01801914269234</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4309309437979412</v>
+        <v>-0.4222068246406767</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.709709709836762</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425332</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.79284219039255</v>
+        <v>-8.771031892499389</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3418733061146257</v>
+        <v>-0.3331491869573613</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.46272245964381</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702417</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.52900532318848</v>
+        <v>-8.507195025295319</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2462220405459052</v>
+        <v>-0.2374979213886408</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.46272245964381</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906232</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.261763522320082</v>
+        <v>-8.239953224426921</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.14115988069792</v>
+        <v>-0.1324357615406555</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.46272245964381</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781952</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.985954358919598</v>
+        <v>-7.964144061026437</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.03113653031118702</v>
+        <v>-0.02241241115392256</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.373703151365077</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567248</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.716886771152619</v>
+        <v>-7.695076473259458</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.07715901094109823</v>
+        <v>0.08588313009836268</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.104635563598098</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487777</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.452826832829823</v>
+        <v>-7.431016534936662</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.1695226701084644</v>
+        <v>0.1782467892657289</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.840575625275301</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83324917230973</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.745747209324985</v>
+        <v>-6.723936911431823</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.4495674858500989</v>
+        <v>0.4582916050073633</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.840575625275301</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.496106179339033</v>
+        <v>-6.474295881445872</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.549767521732321</v>
+        <v>0.5584916408895855</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.59093459528935</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.241564279997958</v>
+        <v>-6.219753982104796</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.6509511026895081</v>
+        <v>0.6596752218467725</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.336392695948274</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.008083057768359</v>
+        <v>-5.986272759875198</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.7522680204192</v>
+        <v>0.7609921395764645</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.102911473718676</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.828374527624486</v>
+        <v>-5.806564229731325</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.82125922216379</v>
+        <v>0.8299833413210544</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.045739969555979</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.6960990539936</v>
+        <v>-5.674288756100439</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.8695368983631715</v>
+        <v>0.8782610175204359</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9134644959250928</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.505499379320447</v>
+        <v>-5.483689081427286</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.9485918289200694</v>
+        <v>0.9573159480773339</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.72286482125194</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.256499580636866</v>
+        <v>-5.234689282743705</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.06109808961716</v>
+        <v>1.069822208774425</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.72286482125194</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077647</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.362089570409971</v>
+        <v>-5.34027927251681</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.8908861641087</v>
+        <v>0.8996102832659645</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8284548110250443</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.380824472528568</v>
+        <v>-5.359014174635407</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.9319365451383477</v>
+        <v>0.9406606642956121</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8284548110250443</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.035050646285567</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.104086297857755</v>
+        <v>-5.358201289023576</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.9930597028287171</v>
+        <v>0.944364830526339</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6466381499151185</v>
+        <v>-0.8598731270342792</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.647067756336496</v>
+        <v>2.57207789422895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.026336660032089</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-4.977193891422685</v>
+        <v>-5.231308882588506</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.035102679149267</v>
+        <v>0.9864078068468887</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5197457434800485</v>
+        <v>-0.7329807205992093</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.71448921394406</v>
+        <v>2.639499351836514</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.019376047936996</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-4.789606383512758</v>
+        <v>-5.043721374678579</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.103177070218145</v>
+        <v>1.054482197915766</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5197457434800485</v>
+        <v>-0.7329807205992093</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.707528601848967</v>
+        <v>2.632538739741421</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.033838402318139</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.5474579900589</v>
+        <v>-4.801572981224721</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.214498781980831</v>
+        <v>1.165803909678452</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5197457434800485</v>
+        <v>-0.7329807205992093</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.72199095623011</v>
+        <v>2.647001094122564</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.028370522777334</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.484228618290552</v>
+        <v>-4.738343609456373</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.234322651147365</v>
+        <v>1.185627778844987</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5197457434800485</v>
+        <v>-0.7329807205992093</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.716523076689305</v>
+        <v>2.641533214581759</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.025868616787911</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.297740925913546</v>
+        <v>-4.551855917079367</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.306415822108745</v>
+        <v>1.257720949806366</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3332580511030423</v>
+        <v>-0.546493028222203</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.825913786126086</v>
+        <v>2.750923924018539</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.033569595025236</v>
+        <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.276591727010103</v>
+        <v>-4.530706718175924</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.322576479907447</v>
+        <v>1.273881607605069</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3121088521995989</v>
+        <v>-0.5253438293187597</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.846304283705477</v>
+        <v>2.771314421597931</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.029350303372287</v>
+        <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.032826285026658</v>
+        <v>-4.286941276192479</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.415863365047876</v>
+        <v>1.367168492745498</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3121088521995989</v>
+        <v>-0.5253438293187597</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.842084992052528</v>
+        <v>2.767095129944982</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.031474617292303</v>
+        <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-3.768798217833398</v>
+        <v>-4.022913208999219</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.523598905845196</v>
+        <v>1.474904033542818</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1102434533836454</v>
+        <v>-0.3234784305028061</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.965328545262116</v>
+        <v>2.89033868315457</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.024216692276005</v>
+        <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.518947823884324</v>
+        <v>-3.773062815050144</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.616281138408528</v>
+        <v>1.56758626610615</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1102434533836454</v>
+        <v>-0.3234784305028061</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.958070620245818</v>
+        <v>2.883080758138272</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.027815815796654</v>
+        <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.215380334880345</v>
+        <v>-3.469495326046166</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.741307257530768</v>
+        <v>1.69261238522839</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1102434533836454</v>
+        <v>-0.3234784305028061</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.961669743766467</v>
+        <v>2.886679881658921</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862991</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.041143321851207</v>
+        <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.141900426028331</v>
+        <v>-3.396015417194151</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.784026727126127</v>
+        <v>1.735331854823749</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.036763544531631</v>
+        <v>-0.2499985216507917</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.019085195132229</v>
+        <v>2.944095333024683</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.765189293763097</v>
+        <v>3.407932146999565</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.091332055832155</v>
+        <v>2.837782550349451</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.141900426028331</v>
+        <v>-3.396015417194151</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.784026727126127</v>
+        <v>1.735331854823749</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.036763544531631</v>
+        <v>-0.2499985216507917</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.084395852818523</v>
+        <v>2.830846347335819</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-2.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.2%</t>
+          <t>494.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.2%</t>
+          <t>-478.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-202.7%</t>
+          <t>-193.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.0%</t>
+          <t>-226.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.9%</t>
+          <t>-138.0%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347059</v>
+        <v>3.29913614634706</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130022</v>
+        <v>3.287377576130023</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178248</v>
+        <v>3.315884374178249</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310986</v>
+        <v>3.284619513310987</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006539</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309428</v>
+        <v>3.311086391309429</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970909</v>
+        <v>3.30471571697091</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330526</v>
+        <v>3.300815818330527</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776682</v>
+        <v>3.500446096776681</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.407932146999565</v>
+        <v>3.407932146999567</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.837782550349451</v>
+        <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.396015417194151</v>
+        <v>-3.166973267597676</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.735331854823749</v>
+        <v>1.825969192278636</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2499985216507917</v>
+        <v>-0.02095637205431655</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.830846347335819</v>
+        <v>3.080541100398865</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240402.xlsx
+++ b/tame_output/ON/bt/strategyON_20240402.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.1%</t>
+          <t>-609.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>494.9%</t>
+          <t>495.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-478.3%</t>
+          <t>-477.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-244.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-160.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-193.6%</t>
+          <t>-193.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-303.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-159.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.1%</t>
+          <t>-203.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-182.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.0%</t>
+          <t>-124.4%</t>
         </is>
       </c>
     </row>
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634706</v>
+        <v>3.299136146347059</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.302366717192751</v>
+        <v>-3.35688590278784</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.818556550016014</v>
+        <v>1.796748875777979</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.2495398976174708</v>
+        <v>-0.2166461100358615</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.99013572263638</v>
+        <v>3.009871995185346</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130023</v>
+        <v>3.287377576130021</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.660017067431099</v>
+        <v>-3.714536253026188</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.671602468576933</v>
+        <v>1.649794794338897</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5742964602742096</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.771651571149629</v>
+        <v>2.791387843698594</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178249</v>
+        <v>3.315884374178248</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.666678007653247</v>
+        <v>-3.721197193248336</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.670711019188333</v>
+        <v>1.648903344950298</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6071902478558189</v>
+        <v>-0.5742964602742096</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.773424497849888</v>
+        <v>2.793160770398854</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207817</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.098483800803034</v>
+        <v>-4.153002986398123</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.484321589395822</v>
+        <v>1.462513915157787</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.7107139567154765</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.697643160001498</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.424916329670778</v>
+        <v>-4.479435515265867</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.342033352850815</v>
+        <v>1.32022567861278</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7931822072226247</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.6364469846993</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006539</v>
+        <v>3.305849539006537</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.426480480781081</v>
+        <v>-4.48099966637617</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.33998828406266</v>
+        <v>1.318180609824624</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7931822072226247</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.635027576355265</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.790106725681395</v>
+        <v>-4.844625911276483</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.201025346336776</v>
+        <v>1.17921767209874</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.8914038440897505</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.582582154469231</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.787679661152676</v>
+        <v>-4.842198846747765</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.201250687154094</v>
+        <v>1.179443012916059</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-0.8917366258969022</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.581637000390772</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.196268438333354</v>
+        <v>-5.250787623928443</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.036576720296582</v>
+        <v>1.014769046058547</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.335245278097124</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.609250922474448</v>
+        <v>-5.663770108069537</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8665691591116054</v>
+        <v>0.8447614848735698</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.330430710568584</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.025642796761446</v>
+        <v>-6.080161982356534</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6980064600056837</v>
+        <v>0.6761987857676481</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.328424761177462</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.40231980729129</v>
+        <v>-6.456838992886379</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5575943464624249</v>
+        <v>0.5357866722243894</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.338683451846141</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.416034671616401</v>
+        <v>-6.47055385721149</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5482079658780754</v>
+        <v>0.5264002916400403</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.334783016991836</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.728859470861381</v>
+        <v>-6.78337865645647</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4214829662350845</v>
+        <v>0.3996752919970494</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.300325403077581</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.333187937046837</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.733672509326718</v>
+        <v>-6.788191694921807</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.423336726778158</v>
+        <v>0.4015290525401225</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.301872037780366</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.336038932154374</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.167021617436954</v>
+        <v>-7.221540803032043</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2459707789996606</v>
+        <v>0.224163104761625</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.301872037780366</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.33201262761997</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.550023006179585</v>
+        <v>-7.604542191774674</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.09266812218102416</v>
+        <v>0.07086044794298862</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.301872037780366</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.331910526298386</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.925008332350862</v>
+        <v>-7.979527517945951</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05475449231605678</v>
+        <v>-0.07656216655409231</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.676857363951644</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>2.10949084656705</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.284538654854863</v>
+        <v>-8.339057840449954</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1932163180196071</v>
+        <v>-0.2150239922576427</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.676857363951644</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>2.1148411498651</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.610938683519876</v>
+        <v>-8.665457869114967</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3158603095284351</v>
+        <v>-0.3376679837664702</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-2.003257392616657</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.92691715262327</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776681</v>
+        <v>3.500446096776682</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.604462536726317</v>
+        <v>-8.658981722321407</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3102281001892422</v>
+        <v>-0.3320357744272777</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.996781245823097</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.933844591321175</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.600771611769906</v>
+        <v>-8.655290797364996</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3087517302066778</v>
+        <v>-0.3305594044447133</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.996781245823097</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.933844591321175</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.80502978709977</v>
+        <v>-8.85954897269486</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3849418032199812</v>
+        <v>-0.4067494774580167</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.124420190437086</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.862774421671424</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.965668813588135</v>
+        <v>-9.020187999183225</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4447148593308912</v>
+        <v>-0.4665225335689267</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.239153663439482</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.798416892354422</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.892198981920686</v>
+        <v>-8.946718167515776</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3999552251704905</v>
+        <v>-0.4217628994085256</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.165683831772033</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.857870492848313</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.067323399307229</v>
+        <v>-9.121842584902319</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4554497713775909</v>
+        <v>-0.4772574456156264</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.340808249158577</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.767351063163903</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.301775493321719</v>
+        <v>-9.356294678916809</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.556449773884983</v>
+        <v>-0.578257448123018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.340808249158577</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.760131898262307</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.589579337858957</v>
+        <v>-9.644098523454048</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6782435024738542</v>
+        <v>-0.7000511767118898</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.628612093695815</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.580777400765988</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.819403785022782</v>
+        <v>-9.873922970617873</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7690574915008281</v>
+        <v>-0.7908651657388637</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-2.791259630765976</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.484304668362448</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.05143270475904</v>
+        <v>-10.10595189035413</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.859175330766218</v>
+        <v>-0.880983005004254</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.853272327954399</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.449790778678509</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.999417190790231</v>
+        <v>-10.05393637638532</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8343787894922921</v>
+        <v>-0.8561864637303271</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.853272327954399</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.45378111436491</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.14108903251435</v>
+        <v>-10.19560821810944</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8925227530806819</v>
+        <v>-0.9143304273187169</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.853272327954399</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.452305887466168</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.23999577297363</v>
+        <v>-10.29451495856872</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9170320390995195</v>
+        <v>-0.9388397133375554</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-2.952179068413674</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.408015253355475</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.04084366573653</v>
+        <v>-10.09536285133162</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8504223298513636</v>
+        <v>-0.8722300040893987</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-2.786856542463861</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.49415763527868</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.814998513017118</v>
+        <v>-9.869517698612206</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7505051957273907</v>
+        <v>-0.7723128699654254</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.744929866876697</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.528892713667186</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.528723700694423</v>
+        <v>-9.583242886289511</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6348561262422536</v>
+        <v>-0.6566638004802883</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.744929866876697</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.530031858223245</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.301927873621089</v>
+        <v>-9.585271507734813</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5415040212508124</v>
+        <v>-0.6548414748963012</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.709709709836762</v>
+        <v>-2.721403071839934</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.553797726609314</v>
+        <v>1.546781709407411</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.01801914269234</v>
+        <v>-9.301362776806064</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4222068246406767</v>
+        <v>-0.5355442782861655</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.709709709836762</v>
+        <v>-2.721403071839934</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.559531430847951</v>
+        <v>1.552515413646048</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.771031892499389</v>
+        <v>-9.054375526613113</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3331491869573613</v>
+        <v>-0.44648664060285</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.46272245964381</v>
+        <v>-2.474415821646982</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.697986518569857</v>
+        <v>1.690970501367954</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.507195025295319</v>
+        <v>-8.790538659409043</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2374979213886408</v>
+        <v>-0.3508353750341295</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.46272245964381</v>
+        <v>-2.474415821646982</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.688103037256949</v>
+        <v>1.681087020055046</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.239953224426921</v>
+        <v>-8.523296858540645</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1324357615406555</v>
+        <v>-0.2457732151861443</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.46272245964381</v>
+        <v>-2.474415821646982</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.686268476757575</v>
+        <v>1.679252459555673</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-7.964144061026437</v>
+        <v>-8.24748769514016</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.02241241115392256</v>
+        <v>-0.1357498647994109</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.373703151365077</v>
+        <v>-2.385396513368248</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.739379746751355</v>
+        <v>1.732363729549452</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-7.695076473259458</v>
+        <v>-7.97842010737318</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.08588313009836268</v>
+        <v>-0.02745432354712563</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.104635563598098</v>
+        <v>-2.116328925601269</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.901488805557036</v>
+        <v>1.894472788355133</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.431016534936662</v>
+        <v>-7.714360169050384</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.1782467892657289</v>
+        <v>0.06490933562024059</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.840575625275301</v>
+        <v>-1.852268987278473</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.046664452388961</v>
+        <v>2.039648435187059</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-6.723936911431823</v>
+        <v>-7.007280545545546</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.4582916050073633</v>
+        <v>0.344954151361875</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.840575625275301</v>
+        <v>-1.852268987278473</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.04387741872866</v>
+        <v>2.036861401526758</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.474295881445872</v>
+        <v>-6.757639515559594</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.5584916408895855</v>
+        <v>0.4451541872440972</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.59093459528935</v>
+        <v>-1.602627957292521</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.194005660608073</v>
+        <v>2.18698964340617</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.219753982104796</v>
+        <v>-6.503097616218518</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.6596752218467725</v>
+        <v>0.5463377682012847</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.336392695948274</v>
+        <v>-1.348086057951445</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.346097621433475</v>
+        <v>2.339081604231573</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-5.986272759875198</v>
+        <v>-6.26961639398892</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.7609921395764645</v>
+        <v>0.6476546859309762</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.102911473718676</v>
+        <v>-1.114604835721847</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.494110783609087</v>
+        <v>2.487094766407184</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-5.806564229731325</v>
+        <v>-6.089907863845047</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.8299833413210544</v>
+        <v>0.7166458876755661</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.045739969555979</v>
+        <v>-1.057433331559151</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.525521475793745</v>
+        <v>2.518505458591842</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-5.674288756100439</v>
+        <v>-5.957632390214161</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.8782610175204359</v>
+        <v>0.7649235638749481</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9134644959250928</v>
+        <v>-0.925157857928264</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.600254246719304</v>
+        <v>2.593238229517401</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.483689081427286</v>
+        <v>-5.767032715541008</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.9573159480773339</v>
+        <v>0.8439784944318456</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.72286482125194</v>
+        <v>-0.7345581832551111</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.717429112210833</v>
+        <v>2.71041309500893</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.234689282743705</v>
+        <v>-5.518032916857427</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.069822208774425</v>
+        <v>0.9564847551289368</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.72286482125194</v>
+        <v>-0.7345581832551111</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.730335453434491</v>
+        <v>2.723319436232589</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.34027927251681</v>
+        <v>-5.623622906630532</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.8996102832659645</v>
+        <v>0.7862728296204762</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8284548110250443</v>
+        <v>-0.8401481730282154</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.53900552997141</v>
+        <v>2.531989512769507</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.359014174635407</v>
+        <v>-5.642357808749129</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.9406606642956121</v>
+        <v>0.8273232106501238</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8284548110250443</v>
+        <v>-0.8401481730282154</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.587549871848497</v>
+        <v>2.580533854646593</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.358201289023576</v>
+        <v>-5.641544923137298</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.944364830526339</v>
+        <v>0.8310273768808507</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8598731270342792</v>
+        <v>-0.8715664890374504</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.57207789422895</v>
+        <v>2.565061877027047</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.231308882588506</v>
+        <v>-5.514652516702228</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.9864078068468887</v>
+        <v>0.8730703532014008</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.7329807205992093</v>
+        <v>-0.7446740826023804</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.639499351836514</v>
+        <v>2.632483334634611</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.043721374678579</v>
+        <v>-5.327065008792301</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.054482197915766</v>
+        <v>0.9411447442702783</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.7329807205992093</v>
+        <v>-0.7446740826023804</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.632538739741421</v>
+        <v>2.625522722539518</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-4.801572981224721</v>
+        <v>-5.084916615338443</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.165803909678452</v>
+        <v>1.052466456032965</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.7329807205992093</v>
+        <v>-0.7446740826023804</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.647001094122564</v>
+        <v>2.639985076920661</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.738343609456373</v>
+        <v>-5.021687243570095</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.185627778844987</v>
+        <v>1.072290325199499</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.7329807205992093</v>
+        <v>-0.7446740826023804</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.641533214581759</v>
+        <v>2.634517197379856</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.551855917079367</v>
+        <v>-4.835199551193089</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.257720949806366</v>
+        <v>1.144383496160878</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.546493028222203</v>
+        <v>-0.5581863902253742</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.750923924018539</v>
+        <v>2.743907906816637</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.530706718175924</v>
+        <v>-4.814050352289645</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.273881607605069</v>
+        <v>1.160544153959581</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5253438293187597</v>
+        <v>-0.5370371913219308</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.771314421597931</v>
+        <v>2.764298404396028</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.286941276192479</v>
+        <v>-4.570284910306201</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.367168492745498</v>
+        <v>1.25383103910001</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5253438293187597</v>
+        <v>-0.5370371913219308</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.767095129944982</v>
+        <v>2.760079112743079</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.022913208999219</v>
+        <v>-4.306256843112941</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.474904033542818</v>
+        <v>1.36156657989733</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3234784305028061</v>
+        <v>-0.3351717925059773</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.89033868315457</v>
+        <v>2.883322665952667</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.773062815050144</v>
+        <v>-4.056406449163866</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.56758626610615</v>
+        <v>1.454248812460662</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3234784305028061</v>
+        <v>-0.3351717925059773</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.883080758138272</v>
+        <v>2.876064740936369</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.469495326046166</v>
+        <v>-3.752838960159888</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.69261238522839</v>
+        <v>1.579274931582902</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3234784305028061</v>
+        <v>-0.3351717925059773</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.886679881658921</v>
+        <v>2.879663864457018</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.396015417194151</v>
+        <v>-3.392052738618802</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.735331854823749</v>
+        <v>1.73691692625389</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2499985216507917</v>
+        <v>0.02561442903510802</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.944095333024683</v>
+        <v>3.109463103436223</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.407932146999567</v>
+        <v>3.412386454591751</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.166973267597676</v>
+        <v>-3.162930902866658</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.825969192278636</v>
+        <v>1.827586138171044</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.02095637205431655</v>
+        <v>0.2057187569508383</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.080541100398865</v>
+        <v>3.216546177801958</v>
       </c>
     </row>
   </sheetData>
